--- a/assets/files/laporan_keuangan.xlsx
+++ b/assets/files/laporan_keuangan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\laragon\www\kursus\assets\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{863A6AEA-B8BB-4158-B137-5BFE225AAD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC7D68C4-886D-49FB-8CB3-3E9F786FFE13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-20610" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -103,7 +103,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="&quot;Rp. &quot;\ #,##0"/>
-    <numFmt numFmtId="167" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="_-&quot;Rp&quot;* #,##0_-;\-&quot;Rp&quot;* #,##0_-;_-&quot;Rp&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -144,12 +144,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,7 +481,7 @@
       <c r="E1" t="s">
         <v>1</v>
       </c>
-      <c r="F1">
+      <c r="F1" s="5">
         <f ca="1">TODAY()</f>
         <v>46190</v>
       </c>
@@ -642,10 +643,10 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F9">
-    <cfRule type="cellIs" priority="2" stopIfTrue="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="lessThan">
+    <cfRule type="cellIs" priority="2" stopIfTrue="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
